--- a/naver-place-crawler/results_health/수원_PT.xlsx
+++ b/naver-place-crawler/results_health/수원_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 권광로 178 한국교직원공제회B1,NEWFIT FITNESS CLUB</t>
+          <t>경기 수원시 팔달구 권광로 178 한국교직원공제회B1,NEWFIT FITNESS CLUB</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjeewmc</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 수원시 권선구 금호로 56 2층 201호, 202호</t>
+          <t>경기 수원시 권선구 금호로 56 2층 201호, 202호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7jrkqs</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 수원시 권선구 금곡로 225 2층 218호</t>
+          <t>경기 수원시 권선구 금곡로 225 2층 218호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w10ddqy</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
+          <t>경기 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5lgg3n</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,7 +1013,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1055,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
+          <t>경기 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdqsyc4</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1149,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
+          <t>경기 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lcl4</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1243,7 +1267,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
+          <t>경기 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ouxt</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1337,7 +1365,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
+          <t>경기 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1362,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mhjg</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>O</t>
@@ -1409,64 +1441,64 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>광교PT 20LINE 에듀하임점</t>
+          <t>더블에스 PT&amp;필라테스&amp;골프 인계점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zero142306@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>email@company.com</t>
-        </is>
-      </c>
+          <t>doublessuwon@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1361-2098</t>
+          <t>0507-1371-0659</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 에듀타운로 101 에듀하임1309오피스텔 102동109호</t>
+          <t>경기 수원시 팔달구 효원로 288 지하1층 지비31호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.20line.co.kr/</t>
+          <t>https://blog.naver.com/doublessuwon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y2ft</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>442</v>
+        <v>286</v>
       </c>
       <c r="Q11" t="n">
-        <v>1726</v>
+        <v>1109</v>
       </c>
       <c r="R11" t="n">
-        <v>2168</v>
+        <v>1395</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>583863184</t>
+          <t>1128582747</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/583863184</t>
+          <t>https://m.place.naver.com/place/1128582747</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1512,29 +1544,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>붐피트니스 헬스 PT 스피닝</t>
+          <t>엔오짐 헬스 PT 파장점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>boomfitness_@naver.com</t>
+          <t>n5gym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1383-9497</t>
+          <t>0507-1497-9592</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 대학로 34 6층 601~606호</t>
+          <t>경기 수원시 장안구 정자로 165 동신프라자 5층 (경기도 수원시 장안구 정자동 429-41 동신프라자 5층)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boomfitness_</t>
+          <t>https://blog.naver.com/n5gym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1554,13 +1586,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w491df</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1569,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1104</v>
+        <v>881</v>
       </c>
       <c r="Q12" t="n">
-        <v>122</v>
+        <v>1515</v>
       </c>
       <c r="R12" t="n">
-        <v>1226</v>
+        <v>2396</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,15 +1620,113 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1085286960</t>
+          <t>1124162460</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085286960</t>
+          <t>https://m.place.naver.com/place/1124162460</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>터닝그라운드 PT&amp;GX</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>j__hyun2362@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1373-2285</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기 수원시 권선구 금곡로196번길 62 401호-402호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/turningground.2022/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44zsv</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>109</v>
+      </c>
+      <c r="R13" t="n">
+        <v>158</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1390013125</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1390013125</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/수원_PT.xlsx
+++ b/naver-place-crawler/results_health/수원_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 수원시 팔달구 권광로 178 한국교직원공제회B1,NEWFIT FITNESS CLUB</t>
+          <t>경기도 수원시 팔달구 권광로 178 한국교직원공제회B1,NEWFIT FITNESS CLUB</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjeewmc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 수원시 권선구 금호로 56 2층 201호, 202호</t>
+          <t>경기도 수원시 권선구 금호로 56 2층 201호, 202호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7jrkqs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -726,10 +718,10 @@
         <v>1252</v>
       </c>
       <c r="Q3" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="R3" t="n">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 수원시 권선구 금곡로 225 2층 218호</t>
+          <t>경기도 수원시 권선구 금곡로 225 2층 218호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w10ddqy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
+          <t>경기도 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5lgg3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,17 +997,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q6" t="n">
         <v>461</v>
       </c>
       <c r="R6" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1071,7 +1055,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
+          <t>경기도 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdqsyc4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1118,10 +1098,10 @@
         <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="R7" t="n">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1169,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
+          <t>경기도 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lcl4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1216,10 +1192,10 @@
         <v>934</v>
       </c>
       <c r="Q8" t="n">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="R8" t="n">
-        <v>3399</v>
+        <v>3397</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1267,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
+          <t>경기도 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1292,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ouxt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1314,10 +1286,10 @@
         <v>1410</v>
       </c>
       <c r="Q9" t="n">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="R9" t="n">
-        <v>4724</v>
+        <v>4723</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1365,7 +1337,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
+          <t>경기도 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1390,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mhjg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>O</t>
@@ -1463,7 +1431,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 수원시 팔달구 효원로 288 지하1층 지비31호</t>
+          <t>경기도 수원시 팔달구 효원로 288 지하1층 지비31호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1488,14 +1456,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y2ft</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1531,202 +1495,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>엔오짐 헬스 PT 파장점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>n5gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1497-9592</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 수원시 장안구 정자로 165 동신프라자 5층 (경기도 수원시 장안구 정자동 429-41 동신프라자 5층)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/n5gym</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w491df</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>881</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1515</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2396</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1124162460</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1124162460</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>터닝그라운드 PT&amp;GX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>j__hyun2362@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1373-2285</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기 수원시 권선구 금곡로196번길 62 401호-402호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/turningground.2022/</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44zsv</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>109</v>
-      </c>
-      <c r="R13" t="n">
-        <v>158</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1390013125</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1390013125</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/수원_PT.xlsx
+++ b/naver-place-crawler/results_health/수원_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="Q3" t="n">
         <v>403</v>
       </c>
       <c r="R3" t="n">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q6" t="n">
         <v>461</v>
       </c>
       <c r="R6" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="R7" t="n">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1409,39 +1409,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더블에스 PT&amp;필라테스&amp;골프 인계점</t>
+          <t>인투짐 재활운동 체형교정 헬스장 광교점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>doublessuwon@naver.com</t>
+          <t>intogym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1371-0659</t>
+          <t>0507-1467-3680</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 효원로 288 지하1층 지비31호</t>
+          <t>경기도 수원시 영통구 광교중앙로266번길 20 201, 202, 203호 인투짐 광교점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doublessuwon</t>
+          <t>https://intogym.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,30 +1471,222 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>463</v>
+      </c>
+      <c r="R11" t="n">
+        <v>658</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1488734997</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1488734997</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>더블에스 PT&amp;필라테스&amp;골프 인계점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>doublessuwon@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1371-0659</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 효원로 288 지하1층 지비31호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/doublessuwon</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>286</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>1109</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1395</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1128582747</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1128582747</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>더 모스트 필라테스 &amp; 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>themost0613n@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1335-0613</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기 수원시 영통구 덕영대로 1531 5층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/themost0613n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4xuc5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>361</v>
+      </c>
+      <c r="R13" t="n">
+        <v>490</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1047929273</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1047929273</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/수원_PT.xlsx
+++ b/naver-place-crawler/results_health/수원_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>보스턴짐 호매실점 헬스 PT</t>
+          <t>우아한번지앤요가필라테스 수원아주대점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bostongym333@naver.com</t>
+          <t>wooahan_13@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1483-8213</t>
+          <t>0507-1311-0711</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 수원시 권선구 금호로 56 2층 201호, 202호</t>
+          <t>경기 수원시 영통구 중부대로 262 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/snJMDG6f</t>
+          <t>https://open.kakao.com/o/sP8y0U1g</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgu3am4</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1254</v>
+        <v>82</v>
       </c>
       <c r="Q3" t="n">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="R3" t="n">
-        <v>1657</v>
+        <v>432</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +734,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1271000764</t>
+          <t>1230105032</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271000764</t>
+          <t>https://m.place.naver.com/place/1230105032</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1987바디케어</t>
+          <t>보스턴짐 수원영통점 헬스 PT전문</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1987bodycare@naver.com</t>
+          <t>bostongym6@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1481-9770</t>
+          <t>0507-1309-7616</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 수원시 권선구 금곡로 225 2층 218호</t>
+          <t>경기도 용인시 기흥구 영통로525번길 24 501호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1987bodycare</t>
+          <t>https://open.kakao.com/o/suF1gohi</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,22 +804,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="Q4" t="n">
-        <v>154</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>273</v>
+        <v>100</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +828,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2075059676</t>
+          <t>2064530422</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075059676</t>
+          <t>https://m.place.naver.com/place/2064530422</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>우아한번지앤요가필라테스 수원아주대점</t>
+          <t>알파짐 수원인계점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wooahan_13@naver.com</t>
+          <t>alphagym01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1311-0711</t>
+          <t>0507-1386-2795</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 수원시 영통구 중부대로 262 3층</t>
+          <t>경기도 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sP8y0U1g</t>
+          <t>https://blog.naver.com/alphagym01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,37 +887,33 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgu3am4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="Q5" t="n">
-        <v>350</v>
+        <v>461</v>
       </c>
       <c r="R5" t="n">
-        <v>432</v>
+        <v>688</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1230105032</t>
+          <t>2023378764</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230105032</t>
+          <t>https://m.place.naver.com/place/2023378764</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>알파짐 수원인계점</t>
+          <t>킹스짐PT 광교앨리웨이점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alphagym01@naver.com</t>
+          <t>kingsgympt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1386-2795</t>
+          <t>0507-1316-5443</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
+          <t>경기도 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/alphagym01</t>
+          <t>https://blog.naver.com/kingsgympt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>461</v>
+        <v>1301</v>
       </c>
       <c r="R6" t="n">
-        <v>688</v>
+        <v>1501</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2023378764</t>
+          <t>1199304438</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023378764</t>
+          <t>https://m.place.naver.com/place/1199304438</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>킹스짐PT 광교앨리웨이점</t>
+          <t>석세스짐&amp;PT 아주대점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kingsgympt@naver.com</t>
+          <t>successgym-a@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1316-5443</t>
+          <t>0507-1433-2409</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
+          <t>경기도 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kingsgympt</t>
+          <t>https://blog.naver.com/successgym-a</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>200</v>
+        <v>934</v>
       </c>
       <c r="Q7" t="n">
-        <v>1301</v>
+        <v>2463</v>
       </c>
       <c r="R7" t="n">
-        <v>1501</v>
+        <v>3397</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1199304438</t>
+          <t>1816064219</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1199304438</t>
+          <t>https://m.place.naver.com/place/1816064219</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>석세스짐&amp;PT 아주대점</t>
+          <t>석세스짐&amp;PT 광교프라이빗점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>successgym-a@naver.com</t>
+          <t>successgym_gp@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1433-2409</t>
+          <t>0507-1365-0726</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
+          <t>경기도 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym-a</t>
+          <t>https://blog.naver.com/successgym_gp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>934</v>
+        <v>1410</v>
       </c>
       <c r="Q8" t="n">
-        <v>2463</v>
+        <v>3313</v>
       </c>
       <c r="R8" t="n">
-        <v>3397</v>
+        <v>4723</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1816064219</t>
+          <t>1026362580</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816064219</t>
+          <t>https://m.place.naver.com/place/1026362580</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>석세스짐&amp;PT 광교프라이빗점</t>
+          <t>밀라노짐 광교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>successgym_gp@naver.com</t>
+          <t>skyboy210@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1365-0726</t>
+          <t>0507-1338-8870</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
+          <t>경기도 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym_gp</t>
+          <t>https://www.instagram.com/milanogym_g</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1274,7 +1274,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1410</v>
+        <v>994</v>
       </c>
       <c r="Q9" t="n">
-        <v>3313</v>
+        <v>2175</v>
       </c>
       <c r="R9" t="n">
-        <v>4723</v>
+        <v>3169</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1026362580</t>
+          <t>1072065011</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1026362580</t>
+          <t>https://m.place.naver.com/place/1072065011</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>밀라노짐 광교점</t>
+          <t>1987바디케어</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>skyboy210@naver.com</t>
+          <t>1987bodycare@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-8870</t>
+          <t>0507-1481-9770</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
+          <t>경기도 수원시 권선구 금곡로 225 2층 218호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/milanogym_g</t>
+          <t>https://blog.naver.com/1987bodycare</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>994</v>
+        <v>119</v>
       </c>
       <c r="Q10" t="n">
-        <v>2175</v>
+        <v>154</v>
       </c>
       <c r="R10" t="n">
-        <v>3169</v>
+        <v>273</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,56 +1392,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1072065011</t>
+          <t>2075059676</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1072065011</t>
+          <t>https://m.place.naver.com/place/2075059676</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인투짐 재활운동 체형교정 헬스장 광교점</t>
+          <t>더블에스 PT&amp;필라테스&amp;골프 인계점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>intogym@naver.com</t>
+          <t>doublessuwon@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1467-3680</t>
+          <t>0507-1371-0659</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 광교중앙로266번길 20 201, 202, 203호 인투짐 광교점</t>
+          <t>경기도 수원시 팔달구 효원로 288 지하1층 지비31호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://intogym.co.kr</t>
+          <t>https://blog.naver.com/doublessuwon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>195</v>
+        <v>286</v>
       </c>
       <c r="Q11" t="n">
-        <v>463</v>
+        <v>1109</v>
       </c>
       <c r="R11" t="n">
-        <v>658</v>
+        <v>1395</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1488734997</t>
+          <t>1128582747</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488734997</t>
+          <t>https://m.place.naver.com/place/1128582747</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1508,29 +1508,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>더블에스 PT&amp;필라테스&amp;골프 인계점</t>
+          <t>엔오짐 헬스 PT 파장점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>doublessuwon@naver.com</t>
+          <t>n5gym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1371-0659</t>
+          <t>0507-1497-9592</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 효원로 288 지하1층 지비31호</t>
+          <t>경기도 수원시 장안구 정자로 165 동신프라자 5층 (경기도 수원시 장안구 정자동 429-41 동신프라자 5층)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doublessuwon</t>
+          <t>https://blog.naver.com/n5gym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1556,7 +1556,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>286</v>
+        <v>882</v>
       </c>
       <c r="Q12" t="n">
-        <v>1109</v>
+        <v>1517</v>
       </c>
       <c r="R12" t="n">
-        <v>1395</v>
+        <v>2399</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,51 +1580,51 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1128582747</t>
+          <t>1124162460</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128582747</t>
+          <t>https://m.place.naver.com/place/1124162460</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>더 모스트 필라테스 &amp; 퍼스널트레이닝</t>
+          <t>터닝그라운드 PT&amp;GX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>themost0613n@naver.com</t>
+          <t>j__hyun2362@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1335-0613</t>
+          <t>0507-1373-2285</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기 수원시 영통구 덕영대로 1531 5층</t>
+          <t>경기도 수원시 권선구 금곡로196번길 62 401호-402호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/themost0613n</t>
+          <t>https://www.instagram.com/turningground.2022/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1639,19 +1639,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4xuc5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1663,13 +1659,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="n">
-        <v>361</v>
+        <v>109</v>
       </c>
       <c r="R13" t="n">
-        <v>490</v>
+        <v>158</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1678,17 +1674,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1047929273</t>
+          <t>1390013125</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1047929273</t>
+          <t>https://m.place.naver.com/place/1390013125</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/수원_PT.xlsx
+++ b/naver-place-crawler/results_health/수원_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -653,39 +653,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>우아한번지앤요가필라테스 수원아주대점</t>
+          <t>보스턴짐 호매실점 헬스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wooahan_13@naver.com</t>
+          <t>bostongym333@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1311-0711</t>
+          <t>0507-1483-8213</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 수원시 영통구 중부대로 262 3층</t>
+          <t>경기도 수원시 권선구 금호로 56 2층 201호, 202호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sP8y0U1g</t>
+          <t>https://open.kakao.com/o/snJMDG6f</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgu3am4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>82</v>
+        <v>1254</v>
       </c>
       <c r="Q3" t="n">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="R3" t="n">
-        <v>432</v>
+        <v>1657</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1230105032</t>
+          <t>1271000764</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230105032</t>
+          <t>https://m.place.naver.com/place/1271000764</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,39 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>보스턴짐 수원영통점 헬스 PT전문</t>
+          <t>우아한번지앤요가필라테스 수원아주대점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bostongym6@naver.com</t>
+          <t>wooahan_13@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1309-7616</t>
+          <t>0507-1311-0711</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 영통로525번길 24 501호</t>
+          <t>경기 수원시 영통구 중부대로 262 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/suF1gohi</t>
+          <t>https://open.kakao.com/o/sP8y0U1g</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -798,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgu3am4</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -809,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>350</v>
       </c>
       <c r="R4" t="n">
-        <v>100</v>
+        <v>432</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2064530422</t>
+          <t>1230105032</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064530422</t>
+          <t>https://m.place.naver.com/place/1230105032</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -845,39 +845,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>알파짐 수원인계점</t>
+          <t>보스턴짐 수원영통점 헬스 PT전문</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alphagym01@naver.com</t>
+          <t>bostongym6@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1386-2795</t>
+          <t>0507-1309-7616</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
+          <t>경기도 용인시 기흥구 영통로525번길 24 501호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/alphagym01</t>
+          <t>https://open.kakao.com/o/suF1gohi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -898,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>227</v>
+        <v>90</v>
       </c>
       <c r="Q5" t="n">
-        <v>461</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>688</v>
+        <v>101</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2023378764</t>
+          <t>2064530422</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023378764</t>
+          <t>https://m.place.naver.com/place/2064530422</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>킹스짐PT 광교앨리웨이점</t>
+          <t>알파짐 수원인계점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kingsgympt@naver.com</t>
+          <t>alphagym01@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1316-5443</t>
+          <t>0507-1386-2795</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
+          <t>경기도 수원시 팔달구 권광로 138 선경센트럴파크 B1층 알파짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kingsgympt</t>
+          <t>https://blog.naver.com/alphagym01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="Q6" t="n">
-        <v>1301</v>
+        <v>461</v>
       </c>
       <c r="R6" t="n">
-        <v>1501</v>
+        <v>688</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1199304438</t>
+          <t>2023378764</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1199304438</t>
+          <t>https://m.place.naver.com/place/2023378764</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>석세스짐&amp;PT 아주대점</t>
+          <t>킹스짐PT 광교앨리웨이점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>successgym-a@naver.com</t>
+          <t>kingsgympt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1433-2409</t>
+          <t>0507-1316-5443</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
+          <t>경기도 수원시 영통구 광교호수공원로 80 K동 2층 257, 258, 259, 260, 261호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym-a</t>
+          <t>https://blog.naver.com/kingsgympt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>934</v>
+        <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>2463</v>
+        <v>1301</v>
       </c>
       <c r="R7" t="n">
-        <v>3397</v>
+        <v>1501</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1816064219</t>
+          <t>1199304438</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816064219</t>
+          <t>https://m.place.naver.com/place/1199304438</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>석세스짐&amp;PT 광교프라이빗점</t>
+          <t>석세스짐&amp;PT 아주대점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>successgym_gp@naver.com</t>
+          <t>successgym-a@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1365-0726</t>
+          <t>0507-1433-2409</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
+          <t>경기도 수원시 팔달구 중부대로 229 4층 석세스짐아주대점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym_gp</t>
+          <t>https://blog.naver.com/successgym-a</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1410</v>
+        <v>934</v>
       </c>
       <c r="Q8" t="n">
-        <v>3313</v>
+        <v>2463</v>
       </c>
       <c r="R8" t="n">
-        <v>4723</v>
+        <v>3397</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1026362580</t>
+          <t>1816064219</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1026362580</t>
+          <t>https://m.place.naver.com/place/1816064219</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>밀라노짐 광교점</t>
+          <t>석세스짐&amp;PT 광교프라이빗점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skyboy210@naver.com</t>
+          <t>successgym_gp@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1338-8870</t>
+          <t>0507-1365-0726</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
+          <t>경기도 수원시 영통구 광교중앙로 180 1동 2층 228호(하동, 광교 효성해링턴타워 레이크)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/milanogym_g</t>
+          <t>https://blog.naver.com/successgym_gp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1274,7 +1274,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>994</v>
+        <v>1410</v>
       </c>
       <c r="Q9" t="n">
-        <v>2175</v>
+        <v>3313</v>
       </c>
       <c r="R9" t="n">
-        <v>3169</v>
+        <v>4723</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1072065011</t>
+          <t>1026362580</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1072065011</t>
+          <t>https://m.place.naver.com/place/1026362580</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1987바디케어</t>
+          <t>밀라노짐 광교점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1987bodycare@naver.com</t>
+          <t>skyboy210@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1481-9770</t>
+          <t>0507-1338-8870</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 수원시 권선구 금곡로 225 2층 218호</t>
+          <t>경기도 수원시 영통구 에듀타운로 24 그린메디칼 B1 광교헬스장 밀라노짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1987bodycare</t>
+          <t>https://www.instagram.com/milanogym_g</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>119</v>
+        <v>994</v>
       </c>
       <c r="Q10" t="n">
-        <v>154</v>
+        <v>2175</v>
       </c>
       <c r="R10" t="n">
-        <v>273</v>
+        <v>3169</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2075059676</t>
+          <t>1072065011</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075059676</t>
+          <t>https://m.place.naver.com/place/1072065011</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1568,10 +1568,10 @@
         <v>882</v>
       </c>
       <c r="Q12" t="n">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="R12" t="n">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1589,100 +1589,6 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>터닝그라운드 PT&amp;GX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>j__hyun2362@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1373-2285</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 수원시 권선구 금곡로196번길 62 401호-402호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/turningground.2022/</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>109</v>
-      </c>
-      <c r="R13" t="n">
-        <v>158</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1390013125</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1390013125</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/수원_PT.xlsx
+++ b/naver-place-crawler/results_health/수원_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjeewmc</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -680,17 +684,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/snJMDG6f</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7jrkqs</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -747,44 +755,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>우아한번지앤요가필라테스 수원아주대점</t>
+          <t>1987바디케어</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wooahan_13@naver.com</t>
+          <t>puhu27@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1311-0711</t>
+          <t>0507-1481-9770</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 수원시 영통구 중부대로 262 3층</t>
+          <t>경기도 수원시 권선구 금곡로 225 2층 218호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sP8y0U1g</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -799,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgu3am4</t>
+          <t>https://talk.naver.com/ct/w10ddqy</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="Q4" t="n">
-        <v>350</v>
+        <v>154</v>
       </c>
       <c r="R4" t="n">
-        <v>432</v>
+        <v>273</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1230105032</t>
+          <t>2075059676</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230105032</t>
+          <t>https://m.place.naver.com/place/2075059676</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -845,44 +853,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>보스턴짐 수원영통점 헬스 PT전문</t>
+          <t>우아한번지앤요가필라테스 수원아주대점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bostongym6@naver.com</t>
+          <t>wooahan_13@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1309-7616</t>
+          <t>0507-1311-0711</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구 영통로525번길 24 501호</t>
+          <t>경기 수원시 영통구 중부대로 262 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/suF1gohi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgu3am4</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -903,17 +915,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>351</v>
       </c>
       <c r="R5" t="n">
-        <v>101</v>
+        <v>433</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2064530422</t>
+          <t>1230105032</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064530422</t>
+          <t>https://m.place.naver.com/place/1230105032</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -966,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/alphagym01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5lgg3n</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q6" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="R6" t="n">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1060,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kingsgympt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdqsyc4</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1098,10 +1118,10 @@
         <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="R7" t="n">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1154,7 +1174,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym-a</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,20 +1184,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lcl4</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,10 +1213,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="Q8" t="n">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="R8" t="n">
         <v>3397</v>
@@ -1248,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/successgym_gp</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,20 +1282,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ouxt</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1286,10 +1314,10 @@
         <v>1410</v>
       </c>
       <c r="Q9" t="n">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="R9" t="n">
-        <v>4723</v>
+        <v>4724</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1342,7 +1370,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/milanogym_g</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,7 +1380,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1362,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mhjg</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>O</t>
@@ -1380,10 +1412,10 @@
         <v>994</v>
       </c>
       <c r="Q10" t="n">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="R10" t="n">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1436,7 +1468,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doublessuwon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1446,20 +1478,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y2ft</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q11" t="n">
         <v>1109</v>
       </c>
       <c r="R11" t="n">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1495,100 +1531,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>엔오짐 헬스 PT 파장점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>n5gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1497-9592</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 수원시 장안구 정자로 165 동신프라자 5층 (경기도 수원시 장안구 정자동 429-41 동신프라자 5층)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/n5gym</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>882</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1518</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2400</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1124162460</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1124162460</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/수원_PT.xlsx
+++ b/naver-place-crawler/results_health/수원_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjeewmc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q2" t="n">
         <v>44</v>
       </c>
       <c r="R2" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,17 +680,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/snJMDG6f</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7jrkqs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -765,7 +757,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>puhu27@naver.com</t>
+          <t>1987bodycare@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -782,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/1987bodycare</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w10ddqy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -846,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -880,17 +868,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sP8y0U1g</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -944,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -978,7 +966,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/alphagym01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +976,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5lgg3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,17 +997,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q6" t="n">
         <v>462</v>
       </c>
       <c r="R6" t="n">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1060,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/kingsgympt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,24 +1070,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdqsyc4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1140,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1154,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/successgym-a</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,24 +1164,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lcl4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1238,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1248,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/successgym_gp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,24 +1258,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ouxt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1314,10 +1286,10 @@
         <v>1410</v>
       </c>
       <c r="Q9" t="n">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="R9" t="n">
-        <v>4724</v>
+        <v>4723</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1336,7 +1308,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1342,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/milanogym_g</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1352,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1390,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mhjg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>O</t>
@@ -1434,105 +1402,383 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더블에스 PT&amp;필라테스&amp;골프 인계점</t>
+          <t>인투짐 재활운동 체형교정 헬스장 광교점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>doublessuwon@naver.com</t>
+          <t>intogym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1371-0659</t>
+          <t>0507-1467-3680</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>경기도 수원시 영통구 광교중앙로266번길 20 201, 202, 203호 인투짐 광교점</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://intogym.co.kr</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>460</v>
+      </c>
+      <c r="R11" t="n">
+        <v>655</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1488734997</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1488734997</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>더블에스 PT&amp;필라테스&amp;골프 인계점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>doublessuwon@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1371-0659</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>경기도 수원시 팔달구 효원로 288 지하1층 지비31호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y2ft</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/doublessuwon</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>285</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>1109</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1394</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1128582747</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1128582747</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>미스트짐 헬스&amp;PT 호매실점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mistgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1430-8341</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 금곡로196번길 35 1층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mist_gym1?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>776</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>370</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1146</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1097676810</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1097676810</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>터닝그라운드 PT&amp;GX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>j__hyun2362@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1373-2285</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 금곡로196번길 62 401호-402호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/turningground.2022/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>109</v>
+      </c>
+      <c r="R14" t="n">
+        <v>158</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1390013125</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1390013125</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
